--- a/backend/Plantillas/orden_compra.xlsx
+++ b/backend/Plantillas/orden_compra.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a9c14fa8f1561f77/Desktop/sistema_contratos/Plantillas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sistema-charaña\backend\Plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{72E81440-BE29-4F27-B2E4-0F2C4BE72E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8ADA2DE-ED2D-46B9-8E3D-D480765E62A4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D76F445-39E7-4697-9158-23D29709EE46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{69706378-BA01-4536-A2F5-9D3D18ED615D}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>ITEM</t>
   </si>
@@ -186,9 +186,6 @@
   </si>
   <si>
     <t>{PRECUNI}</t>
-  </si>
-  <si>
-    <t>{DESCRIPCION}</t>
   </si>
   <si>
     <t>{NITCI}</t>
@@ -760,15 +757,75 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -781,77 +838,17 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2038,46 +2035,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="44"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="35"/>
     </row>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="45"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="46"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="38"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="45"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="46"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="38"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="45"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="46"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="38"/>
     </row>
     <row r="5" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="47"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="49"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="41"/>
     </row>
     <row r="6" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
@@ -2088,7 +2085,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>6</v>
@@ -2101,24 +2098,24 @@
       </c>
     </row>
     <row r="7" spans="2:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="50" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="51" t="s">
+      <c r="B7" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="51"/>
+      <c r="G7" s="43"/>
     </row>
     <row r="8" spans="2:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="52" t="s">
+      <c r="B8" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
       <c r="F8" s="6" t="s">
         <v>8</v>
       </c>
@@ -2131,27 +2128,27 @@
       <c r="B9" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
       <c r="F9" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G9" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
       <c r="F10" s="6" t="s">
         <v>12</v>
       </c>
@@ -2161,52 +2158,52 @@
       </c>
     </row>
     <row r="11" spans="2:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
     </row>
     <row r="12" spans="2:8" ht="24" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="40"/>
-      <c r="E12" s="41"/>
+      <c r="C12" s="48" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="49"/>
+      <c r="E12" s="50"/>
       <c r="F12" s="11" t="s">
         <v>15</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="41.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="33"/>
-      <c r="E13" s="34"/>
+      <c r="C13" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="53"/>
+      <c r="E13" s="54"/>
       <c r="F13" s="11" t="s">
         <v>17</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="35"/>
+      <c r="C14" s="55"/>
       <c r="D14" s="23" t="s">
         <v>19</v>
       </c>
@@ -2217,22 +2214,22 @@
       <c r="G14" s="15"/>
     </row>
     <row r="15" spans="2:8" ht="24.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="55" t="s">
+      <c r="B15" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D15" s="56" t="s">
+      <c r="D15" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="55" t="s">
+      <c r="E15" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="F15" s="56" t="s">
+      <c r="F15" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="56" t="s">
+      <c r="G15" s="31" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2253,14 +2250,12 @@
         <v>37</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="17"/>
-      <c r="C17" s="21" t="s">
-        <v>38</v>
-      </c>
+      <c r="C17" s="21"/>
       <c r="D17" s="18"/>
       <c r="E17" s="18"/>
       <c r="F17" s="24"/>
@@ -2578,74 +2573,64 @@
       </c>
     </row>
     <row r="46" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="57" t="s">
+      <c r="B46" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="C46" s="58"/>
-      <c r="D46" s="58"/>
-      <c r="E46" s="58"/>
-      <c r="F46" s="58"/>
-      <c r="G46" s="59" t="s">
+      <c r="C46" s="57"/>
+      <c r="D46" s="57"/>
+      <c r="E46" s="57"/>
+      <c r="F46" s="57"/>
+      <c r="G46" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="58" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="58"/>
+      <c r="D47" s="58"/>
+      <c r="E47" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="F47" s="59"/>
+      <c r="G47" s="59"/>
+    </row>
+    <row r="48" spans="2:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" s="51"/>
+      <c r="D48" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="E48" s="46"/>
+      <c r="F48" s="46"/>
+      <c r="G48" s="46"/>
+    </row>
+    <row r="49" spans="2:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="C49" s="51"/>
+      <c r="D49" s="46" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="47" spans="2:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="36"/>
-      <c r="D47" s="36"/>
-      <c r="E47" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="F47" s="37"/>
-      <c r="G47" s="37"/>
-    </row>
-    <row r="48" spans="2:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="C48" s="30"/>
-      <c r="D48" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="E48" s="31"/>
-      <c r="F48" s="31"/>
-      <c r="G48" s="31"/>
-    </row>
-    <row r="49" spans="2:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="C49" s="30"/>
-      <c r="D49" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="E49" s="31"/>
-      <c r="F49" s="31"/>
-      <c r="G49" s="31"/>
+      <c r="E49" s="46"/>
+      <c r="F49" s="46"/>
+      <c r="G49" s="46"/>
     </row>
     <row r="50" spans="2:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="51" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B51" s="29"/>
-      <c r="C51" s="29"/>
-      <c r="D51" s="29"/>
-      <c r="E51" s="29"/>
-      <c r="F51" s="29"/>
-      <c r="G51" s="29"/>
+      <c r="B51" s="37"/>
+      <c r="C51" s="37"/>
+      <c r="D51" s="37"/>
+      <c r="E51" s="37"/>
+      <c r="F51" s="37"/>
+      <c r="G51" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B1:G5"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="D48:G48"/>
     <mergeCell ref="B51:G51"/>
     <mergeCell ref="B49:C49"/>
     <mergeCell ref="D49:G49"/>
@@ -2654,6 +2639,16 @@
     <mergeCell ref="B46:F46"/>
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="E47:G47"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="D48:G48"/>
+    <mergeCell ref="B1:G5"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="C9:E9"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="92" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
